--- a/data/00_패널/패널명부.xlsx
+++ b/data/00_패널/패널명부.xlsx
@@ -700,7 +700,11 @@
           <t>coding_ai_complexity_comfort=Comfortable with bounded complex tasks; dev_role_archetype=Full-stack developer; skill_coding=Advanced; skill_debugging=Advanced</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>B-01-1(집필), B-01-2(집필)</t>
+        </is>
+      </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>가상 인물. 실제 인물이 아니다.</t>
@@ -831,7 +835,11 @@
           <t>coding_ai_complexity_comfort=Avoids AI for complexity; coding_ai_usage_frequency=Never used; dev_role_archetype=Other developer; dominant_trait=Balanced; fam_data_science=None; ind_technology=Some exposure; primary_language=Russian; skill_coding=None; skill_debugging=None; tech_savviness=Comfortable</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>B-01-1(집필), B-01-2(집필)</t>
+        </is>
+      </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>가상 인물. 실제 인물이 아니다.</t>
@@ -938,7 +946,11 @@
           <t>coding_ai_usage_frequency=Daily; dev_role_archetype=Data / ML developer; fam_data_science=Expert</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>B-01-1(집필), B-01-2(집필)</t>
+        </is>
+      </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>가상 인물. 실제 인물이 아니다.</t>
@@ -1053,7 +1065,11 @@
           <t>coding_ai_usage_frequency=Tried but not active; dev_role_archetype=Full-stack developer</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>B-01-1(집필), B-01-2(집필)</t>
+        </is>
+      </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>가상 인물. 실제 인물이 아니다.</t>
